--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="110">
   <si>
     <t>Property</t>
   </si>
@@ -54,73 +54,76 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2026-07-29T09:46:30+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院 (https://twcore.mohw.gov.tw/twregistry/)</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 (https://twcore.mohw.gov.tw/twregistry/)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>用於 CarePlan 中標註具體的適性配工或變更作業場所等建議項目。</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>FHIR Version</t>
+  </si>
+  <si>
+    <t>4.0.1</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>complex-type</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>Base Definition</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
     <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2026-07-26T18:45:10+08:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院 (https://twcore.mohw.gov.tw/twregistry/)</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 (https://twcore.mohw.gov.tw/twregistry/)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>用於 CarePlan 中標註具體的適性配工或變更作業場所等建議項目。</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>FHIR Version</t>
-  </si>
-  <si>
-    <t>4.0.1</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>complex-type</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>Base Definition</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
-  </si>
-  <si>
-    <t>Abstract</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -642,23 +645,23 @@
         <v>35</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -671,155 +674,155 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="17.04296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="17.04296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.1015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="12.4765625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.05078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.8984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.1484375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="20.3359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
@@ -835,10 +838,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>22</v>
@@ -850,7 +853,7 @@
         <v>22</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -910,16 +913,16 @@
         <v>32</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>22</v>
@@ -927,10 +930,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -938,10 +941,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>22</v>
@@ -953,13 +956,13 @@
         <v>22</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1010,13 +1013,13 @@
         <v>22</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>22</v>
@@ -1025,15 +1028,15 @@
         <v>22</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1041,10 +1044,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>22</v>
@@ -1056,13 +1059,13 @@
         <v>22</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1101,31 +1104,31 @@
         <v>22</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>22</v>
@@ -1133,10 +1136,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1144,10 +1147,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>22</v>
@@ -1159,16 +1162,16 @@
         <v>22</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1218,13 +1221,13 @@
         <v>22</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>22</v>
@@ -1233,15 +1236,15 @@
         <v>22</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1249,10 +1252,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>22</v>
@@ -1264,13 +1267,13 @@
         <v>22</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1297,11 +1300,11 @@
         <v>22</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>22</v>
@@ -1319,22 +1322,22 @@
         <v>22</v>
       </c>
       <c r="AF6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>用於 CarePlan 中標註具體的適性配工或變更作業場所等建議項目。</t>
+    <t>【依據：勞工健康保護規則附表】用於 CarePlan 中標註具體的適性配工或變更作業場所等建議項目。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-fitness-for-work.xlsx
+++ b/StructureDefinition-ext-fitness-for-work.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
